--- a/model/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/model/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O103"/>
+  <dimension ref="A1:O107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="20"/>
@@ -4756,11 +4756,11 @@
       <c r="B83" s="2" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>学习打开桌灯</t>
+          <t>学习打开投影仪</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -4791,7 +4791,7 @@
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4808,11 +4808,11 @@
       <c r="B84" s="2" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>学习关闭桌灯</t>
+          <t>学习关闭投影仪</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -4860,19 +4860,19 @@
       <c r="B85" s="2" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>打开桌灯</t>
+          <t>打开投影仪</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>163</v>
+        <v>83</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x1E419C2</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4912,19 +4912,19 @@
       <c r="B86" s="2" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>关闭桌灯</t>
+          <t>关闭投影仪</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x1E41A02</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -4964,11 +4964,11 @@
       <c r="B87" s="2" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>学习桌灯亮一点</t>
+          <t>学习打开桌灯</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>161</t>
         </is>
       </c>
     </row>
@@ -5016,11 +5016,11 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>学习桌灯变暖</t>
+          <t>学习关闭桌灯</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -5051,7 +5051,7 @@
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -5068,11 +5068,11 @@
       <c r="B89" s="2" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>桌灯亮一点</t>
+          <t>打开桌灯</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5080,7 +5080,7 @@
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>163</t>
         </is>
       </c>
     </row>
@@ -5120,11 +5120,11 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>桌灯变暖</t>
+          <t>关闭桌灯</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>176</t>
+          <t>164</t>
         </is>
       </c>
     </row>
@@ -5172,11 +5172,11 @@
       <c r="B91" s="2" t="n"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>学习桌灯暗一点</t>
+          <t>学习桌灯亮一点</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -5224,11 +5224,11 @@
       <c r="B92" s="2" t="n"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>学习桌灯变冷</t>
+          <t>学习桌灯变暖</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5276,11 +5276,11 @@
       <c r="B93" s="2" t="n"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>桌灯暗一点</t>
+          <t>桌灯亮一点</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         </is>
       </c>
       <c r="K93" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -5328,11 +5328,11 @@
       <c r="B94" s="2" t="n"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>桌灯变冷</t>
+          <t>桌灯变暖</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -5380,11 +5380,11 @@
       <c r="B95" s="2" t="n"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>学习打开大灯</t>
+          <t>学习桌灯暗一点</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -5432,11 +5432,11 @@
       <c r="B96" s="2" t="n"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>学习关闭大灯</t>
+          <t>学习桌灯变冷</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -5484,19 +5484,19 @@
       <c r="B97" s="2" t="n"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>打开大灯</t>
+          <t>桌灯暗一点</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>0x1E46702</t>
+          <t>0x00</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5519,7 +5519,7 @@
         </is>
       </c>
       <c r="K97" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -5536,15 +5536,15 @@
       <c r="B98" s="2" t="n"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>关闭大灯</t>
+          <t>桌灯变冷</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>0x1E46742</t>
+          <t>0x00</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="K98" s="2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L98" t="inlineStr">
         <is>
@@ -5588,19 +5588,19 @@
       <c r="B99" s="2" t="n"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>回家模式</t>
+          <t>学习打开大灯</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>0x1E4AC01</t>
+          <t>0x00</t>
         </is>
       </c>
       <c r="F99" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -5640,19 +5640,19 @@
       <c r="B100" s="2" t="n"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>出门模式</t>
+          <t>学习关闭大灯</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>0x1E4AC83</t>
+          <t>0x00</t>
         </is>
       </c>
       <c r="F100" s="2" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>178</t>
+          <t>174</t>
         </is>
       </c>
     </row>
@@ -5692,19 +5692,19 @@
       <c r="B101" s="2" t="n"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>打开大灯</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>10001</v>
+        <v>175</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x1E46702</t>
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -5727,34 +5727,36 @@
         </is>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>自定义</t>
         </is>
       </c>
-      <c r="M101" s="2" t="n">
-        <v>10001</v>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="B102" s="2" t="n"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>关闭大灯</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>10002</v>
+        <v>176</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x1E46742</t>
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5777,73 +5779,279 @@
         </is>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>自定义</t>
         </is>
       </c>
-      <c r="M102" s="2" t="n">
-        <v>10002</v>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
       </c>
     </row>
     <row r="103">
       <c r="B103" s="2" t="n"/>
       <c r="C103" t="inlineStr">
         <is>
+          <t>回家模式</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>0x1E4AC01</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="2" t="n"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>出门模式</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>0x1E4AC83</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="2" t="n"/>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="2" t="n"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>10002</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="2" t="n"/>
+      <c r="C107" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D103" s="2" t="n">
+      <c r="D107" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>0x00</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G103" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" t="inlineStr">
-        <is>
-          <t>自定义</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="n">
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>自定义</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
         <v>10003</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88 G89 H89 I89 J89 G90 H90 I90 J90 G91 H91 I91 J91 G92 H92 I92 J92 G93 H93 I93 J93 G94 H94 I94 J94 G95 H95 I95 J95 G96 H96 I96 J96 G97 H97 I97 J97 G98 H98 I98 J98 G99 H99 I99 J99 G100 H100 I100 J100" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="G2 G3 G4 G5 G6 G7 G8 G9 G10 G11 G12 G13 G14 G15 G16 G17 G18 G19 G20 G21 G22 G23 G24 G25 G26 G27 G28 G29 G30 G31 G32 G33 G34 G35 G36 G37 G38 G39 G40 G41 G42 G43 G44 G45 G46 G47 G48 G49 G50 G51 G52 G53 G54 G55 G56 G57 G58 G59 G60 G61 G62 G63 G64 G65 G66 G67 G68 G69 G70 G71 G72 G73 G74 G75 G76 G77 G78 G79 G80 G81 G82 G83 G84 G85 G86 G87 G88 G89 G90 G91 G92 G93 G94 G95 G96 G97 G98 G99 G100 G101 G102 G103 G104 H2 H3 H4 H5 H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23 H24 H25 H26 H27 H28 H29 H30 H31 H32 H33 H34 H35 H36 H37 H38 H39 H40 H41 H42 H43 H44 H45 H46 H47 H48 H49 H50 H51 H52 H53 H54 H55 H56 H57 H58 H59 H60 H61 H62 H63 H64 H65 H66 H67 H68 H69 H70 H71 H72 H73 H74 H75 H76 H77 H78 H79 H80 H81 H82 H83 H84 H85 H86 H87 H88 H89 H90 H91 H92 H93 H94 H95 H96 H97 H98 H99 H100 H101 H102 H103 H104 I2 I3 I4 I5 I6 I7 I8 I9 I10 I11 I12 I13 I14 I15 I16 I17 I18 I19 I20 I21 I22 I23 I24 I25 I26 I27 I28 I29 I30 I31 I32 I33 I34 I35 I36 I37 I38 I39 I40 I41 I42 I43 I44 I45 I46 I47 I48 I49 I50 I51 I52 I53 I54 I55 I56 I57 I58 I59 I60 I61 I62 I63 I64 I65 I66 I67 I68 I69 I70 I71 I72 I73 I74 I75 I76 I77 I78 I79 I80 I81 I82 I83 I84 I85 I86 I87 I88 I89 I90 I91 I92 I93 I94 I95 I96 I97 I98 I99 I100 I101 I102 I103 I104 J2 J3 J4 J5 J6 J7 J8 J9 J10 J11 J12 J13 J14 J15 J16 J17 J18 J19 J20 J21 J22 J23 J24 J25 J26 J27 J28 J29 J30 J31 J32 J33 J34 J35 J36 J37 J38 J39 J40 J41 J42 J43 J44 J45 J46 J47 J48 J49 J50 J51 J52 J53 J54 J55 J56 J57 J58 J59 J60 J61 J62 J63 J64 J65 J66 J67 J68 J69 J70 J71 J72 J73 J74 J75 J76 J77 J78 J79 J80 J81 J82 J83 J84 J85 J86 J87 J88 J89 J90 J91 J92 J93 J94 J95 J96 J97 J98 J99 J100 J101 J102 J103 J104" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99 L100" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90 L91 L92 L93 L94 L95 L96 L97 L98 L99 L100 L101 L102 L103 L104" type="list">
       <formula1>"自定义,随机"</formula1>
     </dataValidation>
   </dataValidations>
